--- a/primary_genes/fisher_int_primary_genes.xlsx
+++ b/primary_genes/fisher_int_primary_genes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/primary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D733B8F-1779-0D48-888F-A8B2442D2ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAB0917-86CC-A24E-91F1-CB8DB57B77D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3500" yWindow="520" windowWidth="22960" windowHeight="16040" xr2:uid="{9A9475FE-0A4E-1D49-86F7-E2B6947CD307}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14280" windowHeight="18000" xr2:uid="{9A9475FE-0A4E-1D49-86F7-E2B6947CD307}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t xml:space="preserve">CpG </t>
   </si>
@@ -44,12 +44,6 @@
     <t xml:space="preserve">Gene </t>
   </si>
   <si>
-    <t>Fisher CI lower</t>
-  </si>
-  <si>
-    <t>Fisher CI upper</t>
-  </si>
-  <si>
     <t>cg03610073</t>
   </si>
   <si>
@@ -93,13 +87,28 @@
   </si>
   <si>
     <t>GSTM1;GSTM1</t>
+  </si>
+  <si>
+    <t>Fisher int upper</t>
+  </si>
+  <si>
+    <t>Fisher int lower</t>
+  </si>
+  <si>
+    <t>CI lower_bound</t>
+  </si>
+  <si>
+    <t>CI upper_bound</t>
+  </si>
+  <si>
+    <t>mean_diff</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -107,13 +116,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -128,8 +151,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,15 +491,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{580CC0E5-9960-764F-9E54-B9D66436D323}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" customWidth="1"/>
     <col min="4" max="4" width="23.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,18 +509,27 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>-2.9537890000000001E-2</v>
@@ -499,13 +537,22 @@
       <c r="D2">
         <v>-7.9000000000000008E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>-2.9489066208019801E-2</v>
+      </c>
+      <c r="F2">
+        <v>-7.9140101204990092E-3</v>
+      </c>
+      <c r="G2">
+        <v>-1.8701538164259349E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>4.0947370000000001E-4</v>
@@ -513,13 +560,22 @@
       <c r="D3">
         <v>4.4673680000000002E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>4.6566565481282401E-4</v>
+      </c>
+      <c r="F3">
+        <v>4.4589013287096397E-3</v>
+      </c>
+      <c r="G3">
+        <v>2.4622834917611409E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>1.568421E-3</v>
@@ -527,13 +583,22 @@
       <c r="D4">
         <v>1.555263E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>1.4876198154931599E-3</v>
+      </c>
+      <c r="F4">
+        <v>1.5644116397419802E-2</v>
+      </c>
+      <c r="G4">
+        <v>8.5658681064564937E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>-2.094737E-2</v>
@@ -541,27 +606,45 @@
       <c r="D5">
         <v>-2.1315790000000002E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
+      <c r="E5">
+        <v>-2.08822037966458E-2</v>
+      </c>
+      <c r="F5">
+        <v>-2.1620653632704501E-3</v>
+      </c>
+      <c r="G5">
+        <v>-1.15221345799581E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
         <v>8.8947370000000002E-4</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>1.9166320000000001E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6" s="2">
+        <v>6.2308692818294003E-4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1.90855794104513E-2</v>
+      </c>
+      <c r="G6">
+        <v>9.8543331693171088E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>2.2263159999999999E-3</v>
@@ -569,27 +652,45 @@
       <c r="D7">
         <v>4.3789469999999997E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
+      <c r="E7">
+        <v>2.3171647372814898E-3</v>
+      </c>
+      <c r="F7">
+        <v>4.4288841979833203E-2</v>
+      </c>
+      <c r="G7">
+        <v>2.3303003358557339E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
         <v>-6.7368419999999998E-3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>-2.3473680000000001E-4</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8" s="2">
+        <v>-6.7223176270956699E-3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-1.5006696589573199E-4</v>
+      </c>
+      <c r="G8">
+        <v>-3.436192296495721E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
         <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
       </c>
       <c r="C9">
         <v>1.810526E-4</v>
@@ -597,19 +698,37 @@
       <c r="D9">
         <v>1.0216070000000001E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
+      <c r="E9">
+        <v>2.20423763105907E-4</v>
+      </c>
+      <c r="F9">
+        <v>1.02641162587917E-2</v>
+      </c>
+      <c r="G9">
+        <v>5.2422700109487907E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2">
         <v>-3.2263159999999999E-2</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>2.7894740000000001E-4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-3.2103027542245498E-2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>6.3764656606576898E-4</v>
+      </c>
+      <c r="G10">
+        <v>-1.5732690488089899E-2</v>
       </c>
     </row>
   </sheetData>

--- a/primary_genes/fisher_int_primary_genes.xlsx
+++ b/primary_genes/fisher_int_primary_genes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/primary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAB0917-86CC-A24E-91F1-CB8DB57B77D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FC7632-D8B7-4C4E-AF9F-CE30790B03BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14280" windowHeight="18000" xr2:uid="{9A9475FE-0A4E-1D49-86F7-E2B6947CD307}"/>
+    <workbookView xWindow="38900" yWindow="500" windowWidth="21080" windowHeight="22780" xr2:uid="{9A9475FE-0A4E-1D49-86F7-E2B6947CD307}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -685,26 +685,26 @@
         <v>-3.436192296495721E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>1.810526E-4</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>1.0216070000000001E-2</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>2.20423763105907E-4</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>1.02641162587917E-2</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>5.2422700109487907E-3</v>
       </c>
     </row>
